--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20485,16 +20485,16 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="O112" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.4476063219830003</v>
+        <v>0.5736314029296703</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>189574</v>
+        <v>189603</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -15431,16 +15431,16 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O84" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.632637572878924</v>
+        <v>2.650425664587565</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O85" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -19693,16 +19693,16 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.569218934676524</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19855,10 +19855,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -20485,16 +20485,16 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="O112" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.5736314029296703</v>
+        <v>0.6344710971797868</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>189603</v>
+        <v>189635</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20485,16 +20485,16 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="O112" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.6344710971797868</v>
+        <v>0.7387677158942723</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>189635</v>
+        <v>189659</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1100</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>655</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>7.271477446541319</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>194</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>3.450889791476427</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>34</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>8.450795244687805</v>
       </c>
@@ -2256,9 +2244,6 @@
       <c r="O10" t="n">
         <v>279</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>4.935442553969462</v>
       </c>
@@ -2652,9 +2637,6 @@
       <c r="O12" t="n">
         <v>419</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>3.915504899450722</v>
       </c>
@@ -3788,9 +3770,6 @@
       <c r="O19" t="n">
         <v>941</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4181,9 +4160,6 @@
       <c r="O21" t="n">
         <v>519</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>5.761674495809076</v>
       </c>
@@ -4477,9 +4453,6 @@
       <c r="O23" t="n">
         <v>193</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>3.433101699767786</v>
       </c>
@@ -4873,9 +4846,6 @@
       <c r="O25" t="n">
         <v>27</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>6.710925635487374</v>
       </c>
@@ -5279,9 +5249,6 @@
       <c r="O27" t="n">
         <v>208</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>3.679469717654653</v>
       </c>
@@ -5675,9 +5642,6 @@
       <c r="O29" t="n">
         <v>411</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>3.840745856024455</v>
       </c>
@@ -6663,9 +6627,6 @@
       <c r="O35" t="n">
         <v>1018</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7056,9 +7017,6 @@
       <c r="O37" t="n">
         <v>543</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>6.028110310644178</v>
       </c>
@@ -7352,9 +7310,6 @@
       <c r="O39" t="n">
         <v>175</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>3.112916049012241</v>
       </c>
@@ -7748,9 +7703,6 @@
       <c r="O41" t="n">
         <v>30</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>7.456584039430417</v>
       </c>
@@ -8154,9 +8106,6 @@
       <c r="O43" t="n">
         <v>162</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>2.86574083778872</v>
       </c>
@@ -8550,9 +8499,6 @@
       <c r="O45" t="n">
         <v>356</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>3.326777432468871</v>
       </c>
@@ -9538,9 +9484,6 @@
       <c r="O51" t="n">
         <v>974</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9931,9 +9874,6 @@
       <c r="O53" t="n">
         <v>512</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>5.683964049815504</v>
       </c>
@@ -10227,9 +10167,6 @@
       <c r="O55" t="n">
         <v>140</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>2.490332839209792</v>
       </c>
@@ -10623,9 +10560,6 @@
       <c r="O57" t="n">
         <v>25</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>6.21382003285868</v>
       </c>
@@ -11029,9 +10963,6 @@
       <c r="O59" t="n">
         <v>220</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>3.891746816750114</v>
       </c>
@@ -11425,9 +11356,6 @@
       <c r="O61" t="n">
         <v>323</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>3.018396378335521</v>
       </c>
@@ -12413,9 +12341,6 @@
       <c r="O67" t="n">
         <v>887</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12954,9 +12879,6 @@
       <c r="O70" t="n">
         <v>137</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>2.436968564083868</v>
       </c>
@@ -13350,9 +13272,6 @@
       <c r="O72" t="n">
         <v>29</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>7.208031238116069</v>
       </c>
@@ -13756,9 +13675,6 @@
       <c r="O74" t="n">
         <v>239</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>4.22785222365126</v>
       </c>
@@ -14152,9 +14068,6 @@
       <c r="O76" t="n">
         <v>366</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>3.420226236751704</v>
       </c>
@@ -15140,9 +15053,6 @@
       <c r="O82" t="n">
         <v>2113</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.6053825574541711</v>
       </c>
@@ -15436,9 +15346,6 @@
       <c r="O84" t="n">
         <v>149</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>2.650425664587565</v>
       </c>
@@ -15832,9 +15739,6 @@
       <c r="O86" t="n">
         <v>33</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>8.202242443373459</v>
       </c>
@@ -16238,9 +16142,6 @@
       <c r="O88" t="n">
         <v>249</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>4.404749806230811</v>
       </c>
@@ -16634,9 +16535,6 @@
       <c r="O90" t="n">
         <v>343</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>3.205293986901188</v>
       </c>
@@ -17030,9 +16928,6 @@
       <c r="O92" t="n">
         <v>520</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>2.259760072147186</v>
       </c>
@@ -17178,9 +17073,6 @@
       <c r="O93" t="n">
         <v>3904</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>1.118510887033168</v>
       </c>
@@ -17326,9 +17218,6 @@
       <c r="O94" t="n">
         <v>4237</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>1.213916656854388</v>
       </c>
@@ -17474,9 +17363,6 @@
       <c r="O95" t="n">
         <v>3922</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>1.123667955672153</v>
       </c>
@@ -17622,9 +17508,6 @@
       <c r="O96" t="n">
         <v>3031</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.8683930580424006</v>
       </c>
@@ -17770,9 +17653,6 @@
       <c r="O97" t="n">
         <v>192</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>3.415313608059144</v>
       </c>
@@ -18166,9 +18046,6 @@
       <c r="O99" t="n">
         <v>221</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>3.909436575008069</v>
       </c>
@@ -18557,16 +18434,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O101" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="R101" t="n">
-        <v>3.588434084460805</v>
+        <v>3.579089204032521</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -18719,10 +18593,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O102" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -18958,9 +18832,6 @@
       <c r="O103" t="n">
         <v>508</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>2.207611762789943</v>
       </c>
@@ -19106,9 +18977,6 @@
       <c r="O104" t="n">
         <v>3107</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.890167347851448</v>
       </c>
@@ -19254,9 +19122,6 @@
       <c r="O105" t="n">
         <v>4346</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.245145572501575</v>
       </c>
@@ -19402,9 +19267,6 @@
       <c r="O106" t="n">
         <v>4467</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>1.279812533908085</v>
       </c>
@@ -19550,9 +19412,6 @@
       <c r="O107" t="n">
         <v>4754</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>1.362039128318566</v>
       </c>
@@ -19693,16 +19552,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O108" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R108" t="n">
-        <v>0.569218934676524</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19855,10 +19711,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O109" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -20089,16 +19945,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="O110" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="R110" t="n">
-        <v>0.2122770990954608</v>
+        <v>1.273662594572764</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -20251,10 +20104,10 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="O111" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -20485,16 +20338,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="O112" t="n">
-        <v>170</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="R112" t="n">
-        <v>0.7387677158942723</v>
+        <v>0.8082987950372627</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20638,9 +20488,6 @@
       <c r="O113" t="n">
         <v>5043</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>1.444838730355601</v>
       </c>
@@ -20709,6 +20556,151 @@
         </is>
       </c>
       <c r="BC113" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>5051</v>
+      </c>
+      <c r="O114" t="n">
+        <v>5051</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1.447130760861817</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -20747,7 +20739,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -20830,7 +20822,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -20840,7 +20832,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -20892,7 +20884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>189659</v>
+        <v>194790</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -17648,13 +17648,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O97" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R97" t="n">
-        <v>3.415313608059144</v>
+        <v>3.450889791476427</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -17807,10 +17807,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O98" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -19552,13 +19552,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="O108" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="R108" t="n">
-        <v>0.6581593932197309</v>
+        <v>0.8004641268888618</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19711,10 +19711,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="O109" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>194790</v>
+        <v>194800</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20338,13 +20338,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="O112" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="R112" t="n">
-        <v>0.8082987950372627</v>
+        <v>0.8865212590731267</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>194800</v>
+        <v>194818</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -19552,13 +19552,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O108" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="R108" t="n">
-        <v>0.8004641268888618</v>
+        <v>0.9071926771407101</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19711,10 +19711,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O109" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -20338,13 +20338,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O112" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R112" t="n">
-        <v>0.8865212590731267</v>
+        <v>0.8908669515195637</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>194818</v>
+        <v>194825</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="O35" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="O36" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -15154,12 +15154,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -15193,84 +15193,92 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>12500</v>
+        <v>1095</v>
       </c>
       <c r="O83" t="n">
-        <v>12500</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.8846963946173433</v>
+        <v>1095</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15297,17 +15305,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15341,22 +15349,39 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>149</v>
+        <v>1095</v>
       </c>
       <c r="O84" t="n">
-        <v>149</v>
-      </c>
-      <c r="R84" t="n">
-        <v>2.650425664587565</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1095</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Gonorrhoea (All Types)</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -15364,6 +15389,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary gonorrhoea notifications across all reported types; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15376,12 +15459,12 @@
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_130</t>
+          <t>SER_CA_ON_PHO_IDTO_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
@@ -15389,47 +15472,47 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15456,17 +15539,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15500,170 +15583,84 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>149</v>
+        <v>12500</v>
       </c>
       <c r="O85" t="n">
-        <v>149</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
-        <v>1</v>
+        <v>12500</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.8846963946173433</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -15695,12 +15692,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15734,13 +15731,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="O86" t="n">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="R86" t="n">
-        <v>8.202242443373459</v>
+        <v>2.650425664587565</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15749,7 +15746,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -15764,7 +15761,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -15772,62 +15769,57 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15859,12 +15851,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15898,29 +15890,29 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="O87" t="n">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_STI</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Lekandi</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -15930,7 +15922,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>laboratory_and_registry_diagnoses</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -15945,7 +15937,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -15980,17 +15972,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>IS_DOH_sti_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -16003,7 +15995,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -16011,62 +16003,57 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16098,12 +16085,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16137,13 +16124,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c r="O88" t="n">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c r="R88" t="n">
-        <v>4.404749806230811</v>
+        <v>8.202242443373459</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -16152,7 +16139,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -16167,65 +16154,70 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -16257,12 +16249,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16296,29 +16288,29 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c r="O89" t="n">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_IS_DOH_STI</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Lekandi</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -16328,7 +16320,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -16343,7 +16335,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -16378,17 +16370,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>IS_DOH_sti_current</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16401,65 +16393,70 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_IS_DOH_STI_GONORRHOEA_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -16491,12 +16488,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16530,13 +16527,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="O90" t="n">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="R90" t="n">
-        <v>3.205293986901188</v>
+        <v>4.404749806230811</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -16545,7 +16542,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -16570,7 +16567,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
@@ -16583,42 +16580,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16650,12 +16647,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16689,29 +16686,29 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="O91" t="n">
-        <v>343</v>
+        <v>249</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonore</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -16736,7 +16733,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -16771,17 +16768,17 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -16804,7 +16801,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -16817,42 +16814,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16884,12 +16881,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16923,81 +16920,95 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>520</v>
+        <v>343</v>
       </c>
       <c r="O92" t="n">
-        <v>520</v>
+        <v>343</v>
       </c>
       <c r="R92" t="n">
-        <v>2.259760072147186</v>
+        <v>3.205293986901188</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17024,17 +17035,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17059,7 +17070,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -17068,81 +17079,170 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>3904</v>
+        <v>343</v>
       </c>
       <c r="O93" t="n">
-        <v>3904</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1.118510887033168</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>343</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17174,12 +17274,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17204,7 +17304,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -17213,13 +17313,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>4237</v>
+        <v>520</v>
       </c>
       <c r="O94" t="n">
-        <v>4237</v>
+        <v>520</v>
       </c>
       <c r="R94" t="n">
-        <v>1.213916656854388</v>
+        <v>2.259760072147186</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17252,42 +17352,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17449,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17358,13 +17458,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>3922</v>
+        <v>3904</v>
       </c>
       <c r="O95" t="n">
-        <v>3922</v>
+        <v>3904</v>
       </c>
       <c r="R95" t="n">
-        <v>1.123667955672153</v>
+        <v>1.118510887033168</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17494,7 +17594,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17503,13 +17603,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3031</v>
+        <v>4237</v>
       </c>
       <c r="O96" t="n">
-        <v>3031</v>
+        <v>4237</v>
       </c>
       <c r="R96" t="n">
-        <v>0.8683930580424006</v>
+        <v>1.213916656854388</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17609,12 +17709,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17639,104 +17739,90 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>194</v>
+        <v>3922</v>
       </c>
       <c r="O97" t="n">
-        <v>194</v>
+        <v>3922</v>
       </c>
       <c r="R97" t="n">
-        <v>3.450889791476427</v>
+        <v>1.123667955672153</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -17763,17 +17849,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17798,179 +17884,90 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>194</v>
+        <v>3031</v>
       </c>
       <c r="O98" t="n">
-        <v>194</v>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
+        <v>3031</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.8683930580424006</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -18002,12 +17999,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -18041,13 +18038,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="O99" t="n">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="R99" t="n">
-        <v>3.909436575008069</v>
+        <v>3.450889791476427</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -18056,7 +18053,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -18076,12 +18073,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -18089,47 +18086,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18161,12 +18158,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18200,29 +18197,29 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="O100" t="n">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -18247,7 +18244,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -18282,17 +18279,17 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -18310,12 +18307,12 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -18323,47 +18320,47 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18395,12 +18392,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18434,13 +18431,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>383</v>
+        <v>221</v>
       </c>
       <c r="O101" t="n">
-        <v>383</v>
+        <v>221</v>
       </c>
       <c r="R101" t="n">
-        <v>3.579089204032521</v>
+        <v>3.909436575008069</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -18449,7 +18446,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -18474,7 +18471,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18487,42 +18484,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18554,12 +18551,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18593,29 +18590,29 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>383</v>
+        <v>221</v>
       </c>
       <c r="O102" t="n">
-        <v>383</v>
+        <v>221</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Gonorré</t>
+          <t>Gonore</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -18640,7 +18637,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -18675,17 +18672,17 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18708,7 +18705,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18721,42 +18718,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18788,12 +18785,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18827,81 +18824,95 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>508</v>
+        <v>383</v>
       </c>
       <c r="O103" t="n">
-        <v>508</v>
+        <v>383</v>
       </c>
       <c r="R103" t="n">
-        <v>2.207611762789943</v>
+        <v>3.579089204032521</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18928,17 +18939,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18963,7 +18974,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18972,81 +18983,170 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>3107</v>
+        <v>383</v>
       </c>
       <c r="O104" t="n">
-        <v>3107</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0.890167347851448</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>383</v>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19078,12 +19178,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -19108,7 +19208,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -19117,13 +19217,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="O105" t="n">
-        <v>4346</v>
+        <v>508</v>
       </c>
       <c r="R105" t="n">
-        <v>1.245145572501575</v>
+        <v>2.207611762789943</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -19156,42 +19256,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19353,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19262,13 +19362,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="O106" t="n">
-        <v>4467</v>
+        <v>3107</v>
       </c>
       <c r="R106" t="n">
-        <v>1.279812533908085</v>
+        <v>0.890167347851448</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19398,7 +19498,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19407,13 +19507,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="O107" t="n">
-        <v>4754</v>
+        <v>4346</v>
       </c>
       <c r="R107" t="n">
-        <v>1.362039128318566</v>
+        <v>1.245145572501575</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19513,12 +19613,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19543,104 +19643,90 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>51</v>
+        <v>4467</v>
       </c>
       <c r="O108" t="n">
-        <v>51</v>
+        <v>4467</v>
       </c>
       <c r="R108" t="n">
-        <v>0.9071926771407101</v>
+        <v>1.279812533908085</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19667,17 +19753,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19702,179 +19788,90 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>51</v>
+        <v>4754</v>
       </c>
       <c r="O109" t="n">
-        <v>51</v>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
+        <v>4754</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1.362039128318566</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19906,12 +19903,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19945,13 +19942,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O110" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="R110" t="n">
-        <v>1.273662594572764</v>
+        <v>0.9071926771407101</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -19960,7 +19957,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -19980,12 +19977,12 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -19993,47 +19990,47 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20065,12 +20062,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20104,29 +20101,29 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="O111" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>Gonore</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -20151,7 +20148,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -20186,17 +20183,17 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -20214,12 +20211,12 @@
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -20227,47 +20224,47 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20299,12 +20296,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20338,81 +20335,95 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="O112" t="n">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="R112" t="n">
-        <v>0.8908669515195637</v>
+        <v>1.273662594572764</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20439,17 +20450,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20483,81 +20494,170 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>5043</v>
+        <v>72</v>
       </c>
       <c r="O113" t="n">
-        <v>5043</v>
-      </c>
-      <c r="R113" t="n">
-        <v>1.444838730355601</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20589,12 +20689,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20619,7 +20719,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20628,13 +20728,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>5051</v>
+        <v>206</v>
       </c>
       <c r="O114" t="n">
-        <v>5051</v>
+        <v>206</v>
       </c>
       <c r="R114" t="n">
-        <v>1.447130760861817</v>
+        <v>0.8952126439660006</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -20667,40 +20767,330 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>5043</v>
+      </c>
+      <c r="O115" t="n">
+        <v>5043</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1.444838730355601</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW114" t="inlineStr">
+      <c r="AW115" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
+      <c r="AX115" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY114" t="inlineStr">
+      <c r="AY115" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
+      <c r="AZ115" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA114" t="inlineStr">
+      <c r="BA115" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB114" t="inlineStr">
+      <c r="BB115" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC114" t="inlineStr">
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>5051</v>
+      </c>
+      <c r="O116" t="n">
+        <v>5051</v>
+      </c>
+      <c r="R116" t="n">
+        <v>1.447130760861817</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -20822,7 +21212,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -20832,7 +21222,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -20852,7 +21242,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -20884,7 +21274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>194825</v>
+        <v>195920</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20728,13 +20728,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="O114" t="n">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="R114" t="n">
-        <v>0.8952126439660006</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>195920</v>
+        <v>195971</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -19942,13 +19942,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O110" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="R110" t="n">
-        <v>0.9071926771407101</v>
+        <v>1.156225961061689</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -20101,10 +20101,10 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O111" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>195971</v>
+        <v>195985</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -17999,12 +17999,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -18038,95 +18038,84 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>194</v>
+        <v>13411</v>
       </c>
       <c r="O99" t="n">
-        <v>194</v>
+        <v>13411</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3.450889791476427</v>
+        <v>0.9491730678570554</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18142,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18197,103 +18186,28 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O100" t="n">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="R100" t="n">
+        <v>3.468677883185068</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -18387,17 +18301,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18431,22 +18345,39 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="O101" t="n">
-        <v>221</v>
-      </c>
-      <c r="R101" t="n">
-        <v>3.909436575008069</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>195</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -18454,6 +18385,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18466,12 +18455,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -18479,47 +18468,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18546,7 +18535,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -18595,98 +18584,23 @@
       <c r="O102" t="n">
         <v>221</v>
       </c>
+      <c r="R102" t="n">
+        <v>3.909436575008069</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Gonore</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD102" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN102" t="b">
-        <v>1</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -18780,17 +18694,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18824,22 +18738,39 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>383</v>
+        <v>221</v>
       </c>
       <c r="O103" t="n">
-        <v>383</v>
-      </c>
-      <c r="R103" t="n">
-        <v>3.579089204032521</v>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>221</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -18847,6 +18778,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>1</v>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18864,7 +18853,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+          <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -18877,42 +18866,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18928,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -18988,98 +18977,23 @@
       <c r="O104" t="n">
         <v>383</v>
       </c>
+      <c r="R104" t="n">
+        <v>3.579089204032521</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Gonorré</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -19173,17 +19087,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -19217,81 +19131,170 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>508</v>
+        <v>383</v>
       </c>
       <c r="O105" t="n">
-        <v>508</v>
-      </c>
-      <c r="R105" t="n">
-        <v>2.207611762789943</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>383</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Gonorré</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GONORRHEA</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19323,12 +19326,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19353,7 +19356,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -19362,13 +19365,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>3107</v>
+        <v>508</v>
       </c>
       <c r="O106" t="n">
-        <v>3107</v>
+        <v>508</v>
       </c>
       <c r="R106" t="n">
-        <v>0.890167347851448</v>
+        <v>2.207611762789943</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19401,42 +19404,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19501,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19507,13 +19510,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>4346</v>
+        <v>3107</v>
       </c>
       <c r="O107" t="n">
-        <v>4346</v>
+        <v>3107</v>
       </c>
       <c r="R107" t="n">
-        <v>1.245145572501575</v>
+        <v>0.890167347851448</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19643,7 +19646,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19652,13 +19655,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>4467</v>
+        <v>4346</v>
       </c>
       <c r="O108" t="n">
-        <v>4467</v>
+        <v>4346</v>
       </c>
       <c r="R108" t="n">
-        <v>1.279812533908085</v>
+        <v>1.245145572501575</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -19788,7 +19791,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19797,13 +19800,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>4754</v>
+        <v>4467</v>
       </c>
       <c r="O109" t="n">
-        <v>4754</v>
+        <v>4467</v>
       </c>
       <c r="R109" t="n">
-        <v>1.362039128318566</v>
+        <v>1.279812533908085</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -19903,12 +19906,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19933,104 +19936,90 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>65</v>
+        <v>4754</v>
       </c>
       <c r="O110" t="n">
-        <v>65</v>
+        <v>4754</v>
       </c>
       <c r="R110" t="n">
-        <v>1.156225961061689</v>
+        <v>1.362039128318566</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20057,7 +20046,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -20101,103 +20090,28 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O111" t="n">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1.227378327896255</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_130</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Gonorrhea</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD111" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG111" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN111" t="b">
-        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -20291,17 +20205,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20335,22 +20249,39 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O112" t="n">
-        <v>72</v>
-      </c>
-      <c r="R112" t="n">
-        <v>1.273662594572764</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>69</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_130</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -20358,6 +20289,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 130.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20370,12 +20359,12 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
+          <t>SER_FI_THL_TTR_130</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -20383,47 +20372,47 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20450,7 +20439,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -20499,98 +20488,23 @@
       <c r="O113" t="n">
         <v>72</v>
       </c>
+      <c r="R113" t="n">
+        <v>1.273662594572764</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>SER_NO_FHI_901_MONTHLY</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_901_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Gonore</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG113" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN113" t="b">
-        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -20684,17 +20598,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20728,81 +20642,170 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>257</v>
+        <v>72</v>
       </c>
       <c r="O114" t="n">
-        <v>257</v>
-      </c>
-      <c r="R114" t="n">
-        <v>1.116842958734282</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Gonore</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_901_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20834,12 +20837,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20873,13 +20876,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>5043</v>
+        <v>257</v>
       </c>
       <c r="O115" t="n">
-        <v>5043</v>
+        <v>257</v>
       </c>
       <c r="R115" t="n">
-        <v>1.444838730355601</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20912,42 +20915,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21012,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -21018,13 +21021,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>5051</v>
+        <v>5043</v>
       </c>
       <c r="O116" t="n">
-        <v>5051</v>
+        <v>5043</v>
       </c>
       <c r="R116" t="n">
-        <v>1.447130760861817</v>
+        <v>1.444838730355601</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -21091,6 +21094,151 @@
         </is>
       </c>
       <c r="BC116" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>5051</v>
+      </c>
+      <c r="O117" t="n">
+        <v>5051</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.447130760861817</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21212,7 +21360,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -21222,7 +21370,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -21274,7 +21422,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>195985</v>
+        <v>209401</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -15731,13 +15731,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O86" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R86" t="n">
-        <v>2.650425664587565</v>
+        <v>2.668213756296206</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O87" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -20090,13 +20090,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O111" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="R111" t="n">
-        <v>1.227378327896255</v>
+        <v>1.316318786439462</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="O112" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -20483,13 +20483,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="O113" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="R113" t="n">
-        <v>1.273662594572764</v>
+        <v>2.405807123081888</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20642,10 +20642,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="O114" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21239,6 +21239,151 @@
         </is>
       </c>
       <c r="BC117" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>4835</v>
+      </c>
+      <c r="O118" t="n">
+        <v>4835</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1.385245937193998</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21277,7 +21422,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -21370,7 +21515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -21422,7 +21567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>209401</v>
+        <v>214306</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20090,13 +20090,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O111" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="R111" t="n">
-        <v>1.316318786439462</v>
+        <v>1.440835428399951</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O112" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214306</v>
+        <v>214313</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20090,13 +20090,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="O111" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="R111" t="n">
-        <v>1.440835428399951</v>
+        <v>1.565352070360441</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="O112" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214313</v>
+        <v>214320</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -18972,13 +18972,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O104" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="R104" t="n">
-        <v>3.579089204032521</v>
+        <v>3.560399443175955</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -19131,10 +19131,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O105" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -20090,13 +20090,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="O111" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="R111" t="n">
-        <v>1.565352070360441</v>
+        <v>2.241299555288813</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="O112" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -20483,13 +20483,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="O113" t="n">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="R113" t="n">
-        <v>2.405807123081888</v>
+        <v>4.104023915845574</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20642,10 +20642,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="O114" t="n">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214320</v>
+        <v>214452</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -20090,13 +20090,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O111" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="R111" t="n">
-        <v>2.241299555288813</v>
+        <v>2.383604288957944</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O112" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -21384,6 +21384,151 @@
         </is>
       </c>
       <c r="BC118" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>gonorrhea</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D033</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Gonorrhea</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>淋病</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>4565</v>
+      </c>
+      <c r="O119" t="n">
+        <v>4565</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1.307889907609225</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21422,7 +21567,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21650,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -21515,7 +21660,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -21567,7 +21712,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>214452</v>
+        <v>219025</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d033/2026-2029.xlsx
+++ b/diseases/d033/2026-2029.xlsx
@@ -43160,13 +43160,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="O230" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="R230" t="n">
-        <v>3.041763682177675</v>
+        <v>3.148492232429523</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -43324,10 +43324,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="O231" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -44836,13 +44836,13 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O240" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R240" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -45000,10 +45000,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O241" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>263895</v>
+        <v>263907</v>
       </c>
     </row>
     <row r="16">
